--- a/docs/specs/Danh_muc_thuoc_bo_sung_nhom_trieu_chung.xlsx
+++ b/docs/specs/Danh_muc_thuoc_bo_sung_nhom_trieu_chung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ALL_PROJECTS\PROJECT_FOR_CUSTOMER\Tuan_Anh\Smart-Medication-Vending\docs\specs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD0388E9-8362-4BC4-B2D4-083C97E3A957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D7F1EC0-C483-4580-8A1D-189B4169D4F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
